--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/new/1889-new.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/new/1889-new.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72E37D56-A59E-43A4-9D3D-620212CE6368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7FC3C53-A69A-4F2E-8978-26495A3C543F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="297">
   <si>
     <t>губ</t>
   </si>
@@ -1795,8 +1795,12 @@
         <f>SUM(N8:AB8)</f>
         <v>356000</v>
       </c>
-      <c r="AE8" s="15"/>
-      <c r="AF8" s="15"/>
+      <c r="AE8" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF8" s="27" t="s">
+        <v>14</v>
+      </c>
       <c r="AH8" s="18"/>
       <c r="AI8" s="18"/>
       <c r="AJ8" s="18"/>
